--- a/data/PConsumoZone.xlsx
+++ b/data/PConsumoZone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eduardo/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eduardo/Documents/Proyectos/Solar/KVA2/KVA-Beta/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{5B096D2D-98DB-1B46-BD65-1220C2816A9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B07250-8445-40F0-B80E-B06F7B660A4D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3929FD-875E-3543-9701-2649A4B61E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>T</t>
   </si>
@@ -52,12 +52,15 @@
   <si>
     <t>Z4</t>
   </si>
+  <si>
+    <t>Z5</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -171,7 +174,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CL"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -689,7 +692,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CL"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="179674120"/>
@@ -748,7 +751,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="en-CL"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="179672072"/>
@@ -790,7 +793,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-CL"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -820,7 +823,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="en-CL"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1725,10 +1728,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1744,8 +1747,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -1761,8 +1767,11 @@
       <c r="E2" s="1">
         <v>0.52</v>
       </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1778,8 +1787,11 @@
       <c r="E3" s="1">
         <v>0.38</v>
       </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1795,8 +1807,11 @@
       <c r="E4" s="1">
         <v>0.22</v>
       </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1812,8 +1827,11 @@
       <c r="E5" s="1">
         <v>0.18</v>
       </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1829,8 +1847,11 @@
       <c r="E6" s="1">
         <v>0.12</v>
       </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1846,8 +1867,11 @@
       <c r="E7" s="1">
         <v>0.08</v>
       </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1863,8 +1887,11 @@
       <c r="E8" s="1">
         <v>7.0000000000000007E-2</v>
       </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1880,8 +1907,11 @@
       <c r="E9" s="1">
         <v>0.08</v>
       </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1897,8 +1927,11 @@
       <c r="E10" s="1">
         <v>0.26</v>
       </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1914,8 +1947,11 @@
       <c r="E11" s="1">
         <v>0.61</v>
       </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1931,8 +1967,11 @@
       <c r="E12" s="1">
         <v>0.71</v>
       </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1948,8 +1987,11 @@
       <c r="E13" s="1">
         <v>0.78</v>
       </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1965,8 +2007,11 @@
       <c r="E14" s="1">
         <v>0.75</v>
       </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1982,8 +2027,11 @@
       <c r="E15" s="1">
         <v>0.79</v>
       </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1999,8 +2047,11 @@
       <c r="E16" s="1">
         <v>0.91</v>
       </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -2016,8 +2067,11 @@
       <c r="E17" s="1">
         <v>0.75</v>
       </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -2033,8 +2087,11 @@
       <c r="E18" s="1">
         <v>0.52</v>
       </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -2050,8 +2107,11 @@
       <c r="E19" s="1">
         <v>0.42</v>
       </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2067,8 +2127,11 @@
       <c r="E20" s="1">
         <v>0.38</v>
       </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -2084,8 +2147,11 @@
       <c r="E21" s="1">
         <v>0.37</v>
       </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -2101,8 +2167,11 @@
       <c r="E22" s="1">
         <v>0.49</v>
       </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -2118,8 +2187,11 @@
       <c r="E23" s="1">
         <v>0.61</v>
       </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -2135,8 +2207,11 @@
       <c r="E24" s="1">
         <v>0.59</v>
       </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2151,6 +2226,9 @@
       </c>
       <c r="E25" s="1">
         <v>0.62</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2160,27 +2238,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Participa xmlns="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53">true</Participa>
-    <TaxCatchAll xmlns="e8d2ff9b-5f5c-45a4-9648-827360dcfaf3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AA99E0A26634CB42BEA9C6EBCCC3F3D9" ma:contentTypeVersion="14" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="80dc5184eb2f50f827e8d206a1eb772e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53" xmlns:ns3="e8d2ff9b-5f5c-45a4-9648-827360dcfaf3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="78e518187f6b49a551e80d0b7b476bda" ns2:_="" ns3:_="">
     <xsd:import namespace="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53"/>
@@ -2393,14 +2450,61 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Participa xmlns="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53">true</Participa>
+    <TaxCatchAll xmlns="e8d2ff9b-5f5c-45a4-9648-827360dcfaf3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7E35159-7F52-4AC2-824D-FAB7B4F8EB5A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E1E0819-D57D-495A-8646-20F645CA5139}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53"/>
+    <ds:schemaRef ds:uri="e8d2ff9b-5f5c-45a4-9648-827360dcfaf3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE572336-1F60-4ECB-9A30-CBD2E0BFA892}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE572336-1F60-4ECB-9A30-CBD2E0BFA892}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E1E0819-D57D-495A-8646-20F645CA5139}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7E35159-7F52-4AC2-824D-FAB7B4F8EB5A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2e14f83a-67ec-4bc9-9da1-ece74f6f9d53"/>
+    <ds:schemaRef ds:uri="e8d2ff9b-5f5c-45a4-9648-827360dcfaf3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>